--- a/Planning de congés 2026(2025).xlsx
+++ b/Planning de congés 2026(2025).xlsx
@@ -69,7 +69,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -116,6 +116,11 @@
       <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0092D050"/>
       </patternFill>
     </fill>
   </fills>
@@ -232,7 +237,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -400,6 +405,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3430,7 +3438,7 @@
       <c r="HL3" s="20" t="n"/>
       <c r="HM3" s="21" t="n"/>
       <c r="HN3" s="21" t="n"/>
-      <c r="HO3" s="55" t="n"/>
+      <c r="HO3" s="63" t="n"/>
       <c r="HP3" s="20" t="n"/>
       <c r="HQ3" s="20" t="n"/>
       <c r="HR3" s="39" t="n"/>
